--- a/salidas/empresas/UBER.xlsx
+++ b/salidas/empresas/UBER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B3" t="n">
@@ -526,7 +538,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B4" t="n">
@@ -551,7 +563,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B5" t="n">
@@ -576,7 +588,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B6" t="n">
@@ -601,7 +613,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B7" t="n">
@@ -626,7 +638,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B8" t="n">
@@ -651,7 +663,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B9" t="n">
@@ -676,7 +688,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B10" t="n">
@@ -701,7 +713,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B11" t="n">
@@ -726,7 +738,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B12" t="n">
@@ -753,7 +765,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B13" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B14" t="n">
@@ -807,7 +819,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B15" t="n">
@@ -834,7 +846,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B16" t="n">
@@ -861,7 +873,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B17" t="n">
@@ -888,7 +900,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B18" t="n">
@@ -915,7 +927,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B19" t="n">
@@ -942,7 +954,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B20" t="n">
@@ -969,7 +981,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B21" t="n">
@@ -996,7 +1008,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B22" t="n">
@@ -1023,7 +1035,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B23" t="n">
@@ -1050,7 +1062,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B24" t="n">
@@ -1077,7 +1089,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B25" t="n">
@@ -1104,7 +1116,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B26" t="n">
@@ -1131,7 +1143,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B27" t="n">
@@ -1158,7 +1170,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B28" t="n">
@@ -1185,7 +1197,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B29" t="n">
@@ -1212,7 +1224,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B30" t="n">
@@ -1239,7 +1251,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B31" t="n">
@@ -1266,7 +1278,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B32" t="n">
@@ -1293,7 +1305,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B33" t="n">
@@ -1320,7 +1332,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B34" t="n">
@@ -1347,7 +1359,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B35" t="n">
@@ -1374,7 +1386,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B36" t="n">
@@ -1401,7 +1413,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B37" t="n">
@@ -1428,7 +1440,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B38" t="n">
@@ -1455,7 +1467,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B39" t="n">
@@ -1482,7 +1494,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B40" t="n">
@@ -1509,7 +1521,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B41" t="n">
@@ -1536,7 +1548,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B42" t="n">
@@ -1563,7 +1575,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B43" t="n">
@@ -1590,7 +1602,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B44" t="n">
@@ -1617,7 +1629,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B45" t="n">
@@ -1644,7 +1656,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B46" t="n">
@@ -1671,7 +1683,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B47" t="n">
@@ -1698,7 +1710,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B48" t="n">
@@ -1725,7 +1737,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B49" t="n">
@@ -1752,7 +1764,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B50" t="n">
@@ -1779,7 +1791,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B51" t="n">
@@ -1806,7 +1818,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B52" t="n">
@@ -1833,7 +1845,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B53" t="n">
@@ -1860,7 +1872,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B54" t="n">
@@ -1887,7 +1899,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B55" t="n">
@@ -1914,7 +1926,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B56" t="n">
@@ -1943,7 +1955,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B57" t="n">
@@ -1972,7 +1984,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B58" t="n">
@@ -2001,7 +2013,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B59" t="n">
@@ -2030,7 +2042,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B60" t="n">
@@ -2059,7 +2071,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B61" t="n">
@@ -2088,7 +2100,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B62" t="n">
@@ -2117,7 +2129,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B63" t="n">
@@ -2146,7 +2158,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B64" t="n">
@@ -2175,7 +2187,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B65" t="n">
@@ -2204,7 +2216,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B66" t="n">
@@ -2233,7 +2245,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B67" t="n">
@@ -2262,7 +2274,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B68" t="n">
@@ -2291,7 +2303,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B69" t="n">
@@ -2320,7 +2332,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B70" t="n">
@@ -2349,7 +2361,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B71" t="n">
@@ -2378,7 +2390,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B72" t="n">
@@ -2407,7 +2419,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B73" t="n">
@@ -2436,7 +2448,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B74" t="n">
@@ -2465,7 +2477,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B75" t="n">
@@ -2494,7 +2506,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B76" t="n">
@@ -2523,7 +2535,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B77" t="n">
@@ -2552,7 +2564,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B78" t="n">
@@ -2581,7 +2593,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B79" t="n">
@@ -2610,7 +2622,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B80" t="n">
@@ -2639,7 +2651,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B81" t="n">
@@ -2668,7 +2680,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B82" t="n">
@@ -2697,7 +2709,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B83" t="n">
@@ -2726,7 +2738,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B84" t="n">
@@ -2755,7 +2767,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B85" t="n">
@@ -2784,7 +2796,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B86" t="n">
@@ -2813,7 +2825,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B87" t="n">
@@ -2842,7 +2854,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B88" t="n">
@@ -2871,7 +2883,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B89" t="n">
@@ -2900,32 +2912,32 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B90" t="n">
-        <v>69.41999816894531</v>
+        <v>69.22000122070312</v>
       </c>
       <c r="C90" t="n">
-        <v>69.41999816894531</v>
+        <v>69.22000122070312</v>
       </c>
       <c r="D90" t="n">
-        <v>315883100</v>
+        <v>330351500</v>
       </c>
       <c r="E90" t="n">
         <v>4.57</v>
       </c>
       <c r="F90" t="n">
-        <v>15.19037159057884</v>
+        <v>15.14660858221075</v>
       </c>
       <c r="G90" t="n">
         <v>2042560121</v>
       </c>
       <c r="H90" t="n">
-        <v>141794519859.7807</v>
+        <v>141386014068.9795</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1546505763783097</v>
+        <v>0.1617340398471434</v>
       </c>
     </row>
   </sheetData>
@@ -2957,75 +2969,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>43620</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -3061,13 +3073,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -3103,13 +3115,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -3145,13 +3157,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -3178,7 +3190,7 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="K5" t="n">
@@ -3191,13 +3203,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>43620</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -3224,7 +3236,7 @@
       <c r="I6" t="n">
         <v>-4.1</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="K6" t="n">
@@ -3237,13 +3249,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -3270,7 +3282,7 @@
       <c r="I7" t="n">
         <v>-6.81</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="K7" t="n">
@@ -3283,13 +3295,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -3316,7 +3328,7 @@
       <c r="I8" t="n">
         <v>-5.279999999999999</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="K8" t="n">
@@ -3329,13 +3341,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -3362,7 +3374,7 @@
       <c r="I9" t="n">
         <v>-6.81</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="K9" t="n">
@@ -3375,13 +3387,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -3408,7 +3420,7 @@
       <c r="I10" t="n">
         <v>-6.25</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="K10" t="n">
@@ -3421,13 +3433,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -3454,7 +3466,7 @@
       <c r="I11" t="n">
         <v>-2.55</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="K11" t="n">
@@ -3467,13 +3479,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -3500,7 +3512,7 @@
       <c r="I12" t="n">
         <v>-2.49</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="K12" t="n">
@@ -3513,13 +3525,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -3546,7 +3558,7 @@
       <c r="I13" t="n">
         <v>-3.86</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="K13" t="n">
@@ -3559,13 +3571,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -3592,7 +3604,7 @@
       <c r="I14" t="n">
         <v>-2.22</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K14" t="n">
@@ -3605,13 +3617,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -3638,7 +3650,7 @@
       <c r="I15" t="n">
         <v>-0.6200000000000001</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="K15" t="n">
@@ -3651,13 +3663,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>44509</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -3684,7 +3696,7 @@
       <c r="I16" t="n">
         <v>-1.28</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>44509</v>
       </c>
       <c r="K16" t="n">
@@ -3697,13 +3709,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -3730,7 +3742,7 @@
       <c r="I17" t="n">
         <v>-0.29</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K17" t="n">
@@ -3743,13 +3755,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -3776,7 +3788,7 @@
       <c r="I18" t="n">
         <v>-3.27</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K18" t="n">
@@ -3789,13 +3801,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -3822,7 +3834,7 @@
       <c r="I19" t="n">
         <v>-5.18</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K19" t="n">
@@ -3835,13 +3847,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -3868,7 +3880,7 @@
       <c r="I20" t="n">
         <v>-4.51</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K20" t="n">
@@ -3881,13 +3893,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -3914,7 +3926,7 @@
       <c r="I21" t="n">
         <v>-4.649999999999999</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="K21" t="n">
@@ -3927,13 +3939,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -3960,7 +3972,7 @@
       <c r="I22" t="n">
         <v>-1.69</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K22" t="n">
@@ -3973,13 +3985,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -4006,7 +4018,7 @@
       <c r="I23" t="n">
         <v>-0.1799999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K23" t="n">
@@ -4019,13 +4031,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -4052,7 +4064,7 @@
       <c r="I24" t="n">
         <v>0.53</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="K24" t="n">
@@ -4065,13 +4077,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -4098,7 +4110,7 @@
       <c r="I25" t="n">
         <v>0.8699999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="K25" t="n">
@@ -4111,13 +4123,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -4144,7 +4156,7 @@
       <c r="I26" t="n">
         <v>0.6299999999999999</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="K26" t="n">
@@ -4157,13 +4169,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -4190,7 +4202,7 @@
       <c r="I27" t="n">
         <v>0.9199999999999999</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="K27" t="n">
@@ -4203,13 +4215,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -4236,7 +4248,7 @@
       <c r="I28" t="n">
         <v>2.02</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K28" t="n">
@@ -4249,13 +4261,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -4282,7 +4294,7 @@
       <c r="I29" t="n">
         <v>4.56</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="K29" t="n">
@@ -4295,13 +4307,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -4328,7 +4340,7 @@
       <c r="I30" t="n">
         <v>5.71</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="K30" t="n">
@@ -4341,13 +4353,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -4374,7 +4386,7 @@
       <c r="I31" t="n">
         <v>5.869999999999999</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K31" t="n">
@@ -4387,13 +4399,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -4420,7 +4432,7 @@
       <c r="I32" t="n">
         <v>7.78</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="K32" t="n">
@@ -4433,13 +4445,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -4466,7 +4478,7 @@
       <c r="I33" t="n">
         <v>4.73</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="K33" t="n">
@@ -4479,13 +4491,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -4512,7 +4524,7 @@
       <c r="I34" t="n">
         <v>4.03</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K34" t="n">
@@ -4525,13 +4537,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -4558,7 +4570,7 @@
       <c r="I35" t="n">
         <v>4.57</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K35" t="n">
@@ -4595,52 +4607,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43607</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>43620</v>
       </c>
       <c r="C2" t="n">
@@ -4669,10 +4681,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43676</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="C3" t="n">
@@ -4701,10 +4713,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43763</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="C4" t="n">
@@ -4733,10 +4745,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="C5" t="n">
@@ -4765,10 +4777,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="C6" t="n">
@@ -4797,10 +4809,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44042</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="C7" t="n">
@@ -4829,10 +4841,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44133</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="C8" t="n">
@@ -4861,10 +4873,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44249</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="C9" t="n">
@@ -4893,10 +4905,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44319</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C10" t="n">
@@ -4925,10 +4937,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44410</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C11" t="n">
@@ -4957,10 +4969,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44503</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>44509</v>
       </c>
       <c r="C12" t="n">
@@ -4989,10 +5001,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44614</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C13" t="n">
@@ -5021,10 +5033,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44683</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C14" t="n">
@@ -5053,10 +5065,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44775</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C15" t="n">
@@ -5085,10 +5097,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C16" t="n">
@@ -5117,10 +5129,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44972</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="C17" t="n">
@@ -5149,10 +5161,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45043</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C18" t="n">
@@ -5181,10 +5193,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45134</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C19" t="n">
@@ -5213,10 +5225,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45232</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="C20" t="n">
@@ -5245,10 +5257,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45334</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="C21" t="n">
@@ -5277,10 +5289,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45418</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="C22" t="n">
@@ -5309,10 +5321,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45506</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="C23" t="n">
@@ -5341,10 +5353,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45593</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C24" t="n">
@@ -5373,10 +5385,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45699</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="C25" t="n">
@@ -5405,10 +5417,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45782</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C26" t="n">
@@ -5437,10 +5449,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45873</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C27" t="n">
@@ -5469,10 +5481,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45960</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="C28" t="n">
@@ -5501,10 +5513,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46063</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="C29" t="n">
@@ -5533,10 +5545,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C30" t="n">
@@ -5565,10 +5577,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C31" t="n">
@@ -5615,12 +5627,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
